--- a/results/part2_step1_preprocessing/preprocessing_results.xlsx
+++ b/results/part2_step1_preprocessing/preprocessing_results.xlsx
@@ -8,13 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Censoring_Overall" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legacy_Validation" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconstruction_Validation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Param_Search_CV" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lost_Demand_By_Product" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Seasonal_Curve" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legacy_Validation" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconstruction_Validation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lost_Demand_By_Product" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Seasonal_Curve" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -833,94 +830,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>pct</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>unconstrained</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3628</v>
-      </c>
-      <c r="C2" t="n">
-        <v>46.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>stock_limited</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2813</v>
-      </c>
-      <c r="C3" t="n">
-        <v>36.1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>stockout</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1329</v>
-      </c>
-      <c r="C4" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>stock_unknown</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>30</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1018,7 +927,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1168,501 +1077,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>trend</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>n_params</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>cv_MAPE_%</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>cv_SE</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>selected</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>shared</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>33</v>
-      </c>
-      <c r="D2" t="n">
-        <v>6.6991</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.0507</v>
-      </c>
-      <c r="F2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>per_product</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>62</v>
-      </c>
-      <c r="D3" t="n">
-        <v>6.7143</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.0616</v>
-      </c>
-      <c r="F3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>shared</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>35</v>
-      </c>
-      <c r="D4" t="n">
-        <v>6.658</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.0296</v>
-      </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>per_product</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>64</v>
-      </c>
-      <c r="D5" t="n">
-        <v>6.6745</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.0389</v>
-      </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>shared</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>37</v>
-      </c>
-      <c r="D6" t="n">
-        <v>6.6614</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.0287</v>
-      </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>per_product</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>66</v>
-      </c>
-      <c r="D7" t="n">
-        <v>6.6747</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>shared</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>39</v>
-      </c>
-      <c r="D8" t="n">
-        <v>6.6592</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.0289</v>
-      </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>per_product</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>68</v>
-      </c>
-      <c r="D9" t="n">
-        <v>6.6728</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>shared</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>41</v>
-      </c>
-      <c r="D10" t="n">
-        <v>6.6636</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.0309</v>
-      </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>per_product</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>70</v>
-      </c>
-      <c r="D11" t="n">
-        <v>6.6769</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.0404</v>
-      </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>shared</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>43</v>
-      </c>
-      <c r="D12" t="n">
-        <v>6.6688</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.0354</v>
-      </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>per_product</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>72</v>
-      </c>
-      <c r="D13" t="n">
-        <v>6.6814</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.0451</v>
-      </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>7</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>shared</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>45</v>
-      </c>
-      <c r="D14" t="n">
-        <v>6.6735</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.0319</v>
-      </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>7</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>per_product</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>74</v>
-      </c>
-      <c r="D15" t="n">
-        <v>6.6863</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.0421</v>
-      </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>8</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>shared</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>47</v>
-      </c>
-      <c r="D16" t="n">
-        <v>6.6821</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.0292</v>
-      </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>8</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>per_product</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>76</v>
-      </c>
-      <c r="D17" t="n">
-        <v>6.6952</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.0396</v>
-      </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>9</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>shared</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>49</v>
-      </c>
-      <c r="D18" t="n">
-        <v>6.6828</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.0269</v>
-      </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>9</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>per_product</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>78</v>
-      </c>
-      <c r="D19" t="n">
-        <v>6.6959</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.0362</v>
-      </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>10</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>shared</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>51</v>
-      </c>
-      <c r="D20" t="n">
-        <v>6.6814</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.0276</v>
-      </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>10</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>per_product</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>80</v>
-      </c>
-      <c r="D21" t="n">
-        <v>6.6945</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.0381</v>
-      </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2280,7 +1695,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2886,176 +2301,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="140" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Topic</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Assumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Forecast latent demand (demand_est), not observed sales; expected sales = min(demand, stock) is derived later.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Unconstrained weeks</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Sales &lt; stock available =&gt; sales equal true demand (stock never binds).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Censored weeks</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Sales = stock available (or 0 with stock 0) =&gt; demand &gt;= sales; reconstructed as max(sales, blend).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Legacy forecast</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Treated as a noisy (~10%), unbiased measure of demand; validated on unconstrained weeks only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Selection effect</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Unconstrained weeks are slightly biased to lower-demand weeks (demand &lt; stock); the blend weight is a low-risk 1-parameter fit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Seasonal model</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Log-linear, one shared Fourier seasonal curve for all products (justified by profile correlation) + product level + trend; K and trend structure tuned by blocked CV.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Calendar</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Synthetic dates (week 1 = 2020-01-06); 'month'/'season' labels are illustrative, week-of-year (1-52) is the real cycle position.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Forecast horizon</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>26 weeks after week 260 (weeks 261-286); price / COGS held at their last-13-week mean for scenarios; future stock is unknown.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>